--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>66.02767387734258</v>
+        <v>10.72949700506817</v>
       </c>
       <c r="D2" t="n">
-        <v>64.8932109999961</v>
+        <v>10.54514678749937</v>
       </c>
       <c r="E2" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F2" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.77003231367819</v>
+        <v>10.85013025097271</v>
       </c>
       <c r="D3" t="n">
-        <v>31.53441891970743</v>
+        <v>5.124343074452458</v>
       </c>
       <c r="E3" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F3" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.92357344471507</v>
+        <v>4.8625806847662</v>
       </c>
       <c r="D4" t="n">
-        <v>30.03887263480599</v>
+        <v>4.881316803155973</v>
       </c>
       <c r="E4" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F4" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.0744955760995</v>
+        <v>6.024605531116169</v>
       </c>
       <c r="D5" t="n">
-        <v>8.74642784226795</v>
+        <v>1.421294524368542</v>
       </c>
       <c r="E5" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F5" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.439648492507071</v>
+        <v>1.208942880032399</v>
       </c>
       <c r="D6" t="n">
-        <v>7.344411626921288</v>
+        <v>1.193466889374709</v>
       </c>
       <c r="E6" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F6" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.3315981739628</v>
+        <v>6.066384703268955</v>
       </c>
       <c r="D7" t="n">
-        <v>32.31098884280702</v>
+        <v>5.250535686956141</v>
       </c>
       <c r="E7" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F7" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.30015489988688</v>
+        <v>6.061275171231619</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>6.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F8" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.57647633244198</v>
+        <v>7.893677404021822</v>
       </c>
       <c r="D9" t="n">
-        <v>29.01053448509888</v>
+        <v>4.714211853828568</v>
       </c>
       <c r="E9" t="n">
-        <v>18.16134500097088</v>
+        <v>2.951218562657768</v>
       </c>
       <c r="F9" t="n">
-        <v>16.73359383577658</v>
+        <v>2.719208998313694</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
